--- a/backend/exports/yandaojie/deliverables/packets_validity/packet_科学_T1.xlsx
+++ b/backend/exports/yandaojie/deliverables/packets_validity/packet_科学_T1.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="编码手册" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标注表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分SOP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对齐练习" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标注表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +48,11 @@
     <font>
       <name val="Arial"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -132,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,25 +182,31 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -856,6 +869,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>评分流程 SOP（标注前必读）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>1. 读手册</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>先读「编码手册」sheet，重点记 ②辩护深度 的 5 档定义与 4 条判别规则。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2. 对齐练习(norming)</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>三位老师各自**独立**标完「对齐练习」sheet 的 8 条 → 与主持人手中的 gold key 逐条对照 → 讨论分歧（重点：对标签错机制 vs 空洞、语言科→难判断）→ 统一理解。对齐后再开始正式标注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>3. 正式标注</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>在「标注表」逐行**独立**标注 ①MC视角 ②辩护深度 ③揭示了什么(引用一句) ④信心。三位老师互不商量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>①只看学生说出的答案；②看整段辩护；二者**独立**。只要追问下机制站不住，就**不算“扎实”**（哪怕答案全对）。信息不足 → 难判断 + 低信心。语言科若无可辩护的机制 → 难判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>节奏</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>每条约 2–3 分钟；进入下一条后不回改上一条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>交回文件；研究者计算评分员信度(κ)。若某维度 κ&lt;0.6，回到 norming 再对齐一轮后重标该批。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>课题</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>本课学习目标</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>学生反思（输入）</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>完整辩护对话（AI追问 → 学生作答，逐轮）</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>①MC视角
+(只看答案/结论)</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>②辩护深度
+(看完整辩护)</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>③辩护揭示了什么(引用一句)</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>④信心(1–5)</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>评分老师</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>数6</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对前后的数同时乘或除以一个相同的数，图形形状不变。」</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你在方格纸上放大图形时，具体是怎么改变数对的？请用小猫乐乐的一个点举例说明变化前后的数对。
+    学生：「(0,2)同时乘2得（0，4）」
+R2 AI：你把(0,2)乘2变成了(0,4)，那么小猫的其他点应该怎么变化？请解释原因。
+    学生：「前后同时乘2，因为都乘2，图形不变」
+R3 AI：你刚才说“图形不变”，但放大后的图形应该变大了呀，你觉得这里的“图形不变”是什么意思？
+    学生：「（空）」
+R4 AI：你刚才提到“图形不变”，但放大后的图形大小改变了，为什么还说图形不变呢？请解释一下你的想法。
+    学生：「是图形形状不变」</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>数2</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对里的两个数字同时乘一个不为零的数字与原来图形相向」；疑问=「无」</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你说“数对里的两个数字同时乘一个不为零的数字与原来图形相向”，这里的“相向”是指图形形状不变吗？如果我们将小猫乐乐每个点的数对都乘2，画出新图形后，新图形和原图形相比到底发生了什么变化？为什么会这样？
+    学生：「是原图形的每条线段按比例放大到原来的二分之一」
+R2 AI：你刚才说将每个点的数对乘2后，新图形的每条线段按比例放大到原来的二分之一，为什么是二分之一而不是2倍呢？请解释你的想法。
+    学生：「说错了不好意思，是两倍」
+R3 AI：你刚才说乘2后图形变成原来的两倍，那如果想将小猫乐乐缩小到原来的一半，你会如何改变数对？为什么这样做？
+    学生：「将数对的两个数字同时乘二分之一，因为这样会按比例缩小，不影响形状」
+R4 AI：你在反思中提到“乘一个不为零的数字”，如果乘0，会画出什么图形？请解释你的想法。
+    学生：「任何数字乘0都等于0，将两个数字都乘0就没有图形了」
+R4 AI：你刚才说乘0后就没有图形了，但如果所有点都在(0,0)，在方格纸上我们能画出什么？请解释你的想法。
+    学生：「任何数字乘0都等于0，将两个数字都乘0就没有图形了」</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>数1</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对的横轴，纵轴和数对的表示方法」</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你已经知道数对可以表示方格纸上的点，如果要把小猫乐乐的图形放大到原来的2倍，你认为每个点的数对应该怎样变化？请解释你的想法。
+    学生：「如果是(2,8),变成（4，16）」
+R2 AI：你提到将数对的两个数都乘以2，这样新的点位置有什么变化？画出的新图形大小和形状会怎样？请解释你的理由。
+    学生：「会向上向右2格，」</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="22" t="n"/>
+      <c r="J4" s="21" t="n"/>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>数29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「横轴与纵轴，在数对中横轴与纵轴同时乘或除以一个相同的数（0除外）得到的图形与图形最像。」</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你说横轴与纵轴同时乘或除以一个相同的数得到的图形最像，请解释为什么这样做得到的图形会最像呢？
+    学生：「因为当设前项为x，后项为y,」
+R2 AI：你说“因为当设前项为x，后项为y,”，请把你的想法说完，解释为什么横轴和纵轴同时乘或除以相同的数，图形就会最像？
+    学生：「（空）」
+R3 AI：你上次写到“因为当设前项为x，后项为y,”，请以小猫图形上的一个点为例，说明为什么x和y同时乘相同数后，新图形与原图形形状相似？
+    学生：「（空）」
+R3 AI：你刚才说‘当第一项乘一个数，第二项也乘一个相同的数，前后可以约分，就是x，’，请你用一个具体的点，比如小猫身上的点(3,2)，把这句话说完，解释为什么这样做就能让图形形状不变？
+    学生：「（空）」
+R4 AI：你提到“前后可以约分，就是x”，请用小猫身上的点(3,2)为例，把这句话说完，解释把(3,2)的横纵坐标都乘2后，新点(6,4)与原点相比，为什么图形形状不变？
+    学生：「因为6除以2等于3 ，4除以2等于2，他们都是除以一个相同的数得出（3，2）」</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>数15</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「如何观察不同数对
+找数对中不同的规律
+根据规律画出图案」</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到通过找数对的规律来画出图案，请具体说说，你是怎样从原图数对得到放大的数对的？
+    学生：「观察前后的数找倍数关系」
+R2 AI：你提到“观察前后的数找倍数关系”，请以小猫的一个点为例，具体说说你是怎样用这个倍数关系从原点对得到新点对的？
+    学生：「若前面的数对为（2，3），后面的为（4，6），」
+R3 AI：你举的例子中（4,6）是（2,3）的两倍，那么小猫的其他点是否也都用了相同的两倍关系？请以另一个点为例说明。
+    学生：「有，比如：（3，5）和（6，10）为两倍关系」
+R4 AI：你通过乘以2得到了放大后的数对并画出了新图形，请问画出的放大图与原来的小猫像吗？结合你的画图经验说明理由。
+    学生：「像，因为按照等比例放大或缩小，图形的整体会比较相似。」
+R4 AI：你说等比例放大图形会相似，那么如果要把小猫缩小到原来的一半，数对应该怎么变化？请以（6,10）为例说明。
+    学生：「像，因为按照等比例放大或缩小，图形的整体会比较相似。」</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>数24</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>《可爱的小猫》</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>1) 经历将“小猫乐乐”在方格纸上利用“数对”放大的探索过程，通过“填一填”“画一画”等活动，体会用“数对”的变化进行图形的放大与缩小的方法，积累数学活动经验。
+2) 在活动中体验图形的多种变化，感受在方格纸上利用“数对”进行图形的放大与缩小的趣味性，激发数学兴趣。</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「数对各点按等比例扩大或缩小才与原图形最像」；疑问=「无」</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到“数对各点按等比例扩大或缩小才与原图形最像”，那请结合小猫乐乐的某个点，说说你是怎样用数对进行等比例放大的？
+    学生：「例如a点 它对应的数对是（x，y） 必须是（bx，by）」
+R2 AI：你用“(bx, by)”放大了a点，那么小猫乐乐身上其他点的数对也需要乘以同一个b吗？如果b不一样会发生什么？
+    学生：「（空）」
+R3 AI：你在反思中说‘数对各点按等比例扩大或缩小才与原图形最像’，那么如果小猫乐乐的不同点乘以不同的b，图形会变成什么样？请结合你的反思解释一下。
+    学生：「因为第一个数是都乘2 而第二个不是这样」
+R3 AI：你用数对举例说明一下，比如原图有两点A(1,1)和B(1,3)，如果A放大为(2,2)而B放大为(2,5)，它们的边长比例与原图相比怎么不同了？
+    学生：「因为第一个数是都乘2 而第二个不是这样」
+R3 AI：你说第一个数都乘2，第二个不是这样，那么B点的纵坐标从3变成5是乘以了几？这导致竖直边AB的长度比原来扩大了多少倍？
+    学生：「因为第一个数是都乘2 而第二个不是这样」</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>科2</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「我学到了物质的变化有化学变化也有物理变化，化学变化是产生了新的物质，物理变化是没有产生新物质」</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你提到化学变化产生新物质，物理变化没有，那么你能从厨房里找出一个物理变化和一个化学变化的例子，并用这个标准解释为什么这样分类吗？
+    学生：「比如化学变化有鸡蛋从神的变化成sh」
+R2 AI：你提到了鸡蛋从“神”的变化成“sh”，老师不太确定你想说的是不是“生的变成熟的”？请你完整地说一说鸡蛋煮熟的过程是否符合产生新物质的标准，为什么？
+    学生：「（空）」
+R3 AI：你上次说鸡蛋从生的变成熟的，请你现在完整地解释一下：鸡蛋煮熟后有没有产生新物质？为什么？
+    学生：「产生了因为他产生了气味」
+R4 AI：你说鸡蛋煮熟产生了气味，所以觉得产生了新物质。但气味也可能是鸡蛋里原来的物质受热挥发出来的。你怎么判断这个气味是煮的过程里新生成的物质，而不是原来就有的呢？
+    学生：「（空）」
+R5 AI：你还没回答气味是原有的还是新生成的，那换个角度想一想：除了气味，鸡蛋煮熟前后还有什么明显的变化？这些变化能不能说明产生了新物质？
+    学生：「比如它产生了发热和蛋白从变白」</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>英20</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Unit 6 Summer Vacation</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>1) 通过听、说、读、写等形式的语言活动，帮助学生复习前几册有关Travel Plan, Winter Vacation, Special Days, Transportation和Around the World等话题的重点词汇和功能句，引导学生综合运用所学语言知识和技能进行交流。
+2) 引导学生就所听材料或所读短文的内容与他人展开对话交流。
+3) 引导学生仿照阅读文段，按相应的提示或要求写几个意义连贯的句子。</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>目标1：学到=「学到了做暑假计划」</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>R1 AI：你的暑假计划是什么？请用英语回答。
+    学生：「shanghai」
+R1 AI：你说的“Play”，具体要去哪里玩呢？请用英语回答。
+    学生：「shanghai」
+R2 AI：你在上海具体要做什么？请用英语回答。
+    学生：「play」
+R3 AI：你一直说“play”，能详细说说你在上海打算玩什么娱乐项目或运动吗？请用英语回答。
+    学生：「iat」
+R4 AI：你怎么去上海？请用英语回答。
+    学生：「by plane」</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="G2:G9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"已掌握,部分,未掌握"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"扎实,对标签错机制,空洞或猜对,完全不懂,难判断"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -874,99 +1500,99 @@
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>学生</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>课题</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>本课学习目标</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>学生反思（输入）</t>
         </is>
       </c>
-      <c r="F1" s="16" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>完整辩护对话（AI追问 → 学生作答，逐轮）</t>
         </is>
       </c>
-      <c r="G1" s="16" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>①MC视角
 (只看答案/结论)</t>
         </is>
       </c>
-      <c r="H1" s="16" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>②辩护深度
 (看完整辩护)</t>
         </is>
       </c>
-      <c r="I1" s="16" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>③辩护揭示了什么(引用一句)</t>
         </is>
       </c>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>④信心(1–5)</t>
         </is>
       </c>
-      <c r="K1" s="16" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>评分老师</t>
         </is>
       </c>
-      <c r="L1" s="16" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>科8</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「生物的多样性」</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>R1 AI：在厨房里，请你举出一个会产生新物质的变化和一个不会产生新物质的变化，并解释你是根据什么标准来区分的。
     学生：「米饭」
@@ -980,47 +1606,47 @@
     学生：「没」</t>
         </is>
       </c>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="20" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L2" s="22" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="21" t="n"/>
+      <c r="I2" s="22" t="n"/>
+      <c r="J2" s="21" t="n"/>
+      <c r="K2" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L2" s="24" t="n"/>
     </row>
     <row r="3" ht="150" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>科11</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了化学变化，物理变化，化学变化产生了新物质，物理变化不产生新物质」</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能以厨房里的一种现象为例，说说它是物理变化还是化学变化，并解释你为什么这样判断吗？
     学生：「米饭蒸熟了是化学变化」
@@ -1034,48 +1660,48 @@
     学生：「不会，因为土就不会」</t>
         </is>
       </c>
-      <c r="G3" s="19" t="n"/>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="20" t="n"/>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L3" s="22" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="21" t="n"/>
+      <c r="K3" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="n"/>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>科14</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化是产生新物质
 物理变化没有产生新物质」</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>R1 AI：煎蛋是物理变化还是化学变化？请用是否产生新物质来判断并解释。
     学生：「物理变化」
@@ -1089,47 +1715,47 @@
     学生：「蛋青变蛋白」</t>
         </is>
       </c>
-      <c r="G4" s="19" t="n"/>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="19" t="n"/>
-      <c r="K4" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L4" s="22" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="22" t="n"/>
+      <c r="J4" s="21" t="n"/>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L4" s="24" t="n"/>
     </row>
     <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>科22</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物理变化未产生新物质和化学变化产生新物质」；疑问=「不知道那些例子」</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能分别举出一个厨房里的物理变化和化学变化的例子，并说说为什么这么分类吗？
     学生：「素菜切片」
@@ -1143,47 +1769,47 @@
     学生：「气味更香颜色更黄」</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="19" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L5" s="22" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="21" t="n"/>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="n"/>
     </row>
     <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>科40</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物质会发生物理变化和化学变化」；疑问=「水是什么无物质」</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在反思中提到水，那水烧开变成水蒸气，是物理变化还是化学变化？请用是否产生新物质来解释。
     学生：「未产生新物质，只是将水转化成水蒸气」
@@ -1197,47 +1823,47 @@
     学生：「没产生xing'wu'zh」</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n"/>
-      <c r="H6" s="19" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L6" s="22" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L6" s="24" t="n"/>
     </row>
     <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>科16</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「梅兰芳被迫报名缴费破密集破解恐怕高科技xd」；疑问=「u体育教育玉兔语言兔兔鱼鱼鱼雨衣vu看看与i辅以研讨会在任天堂然后发货人太搞笑人妖号让他死刑复核一下他输入用户，9了。8䣡i与解封一具遗体于寄托于突出贴图吐槽与i液体崔uiu有哦iuiui故意囧iu尽快把关于uuuuuuuuuuuu衣裤偶咯卡具骷髅比较活泼i看力破IP破IP【噢破破批判oi呸呸呸」</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能说出厨房里正在发生的一些变化吗？比如水烧开或煎鸡蛋，并试着说说这些变化有什么不同？
     学生：「上午」
@@ -1252,47 +1878,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="n"/>
     </row>
     <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>科38</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物理变化与现时变换」</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到物理变化与化学变化，请举一个厨房里发生的例子，并说说你是怎么判断它有没有产生新物质的。
     学生：「素菜切块w」
@@ -1306,47 +1932,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="19" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="19" t="n"/>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L8" s="22" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L8" s="24" t="n"/>
     </row>
     <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>科15</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「各种物质都在不断地变化它与生活息息相关有的是物理变化有的是化学变化。米饭经过蒸熟才会变成饭」</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到“米饭经过蒸熟才会变成饭”，你觉得这个变化过程中有新的物质产生吗？为什么？
     学生：「没有因为它是它是物理变化」
@@ -1360,47 +1986,47 @@
     学生：「本来就有」</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L9" s="22" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="n"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>科12</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「产生新物质是化学反应；没产生是物理反应」；疑问=「暂无」</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>R1 AI：在厨房里，煎鸡蛋时蛋清从透明变白，这属于物理变化还是化学变化？请用你提到的‘是否产生新物质’标准来解释。
     学生：「化学反应」
@@ -1414,47 +2040,47 @@
     学生：「气味变化」</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L10" s="24" t="n"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>科17</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「产生新物质是化学变化」</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到产生新物质是化学变化，那你能举一个厨房里产生新物质的化学变化的例子，并说明为什么它是化学变化吗？
     学生：「鸡蛋熟了」
@@ -1468,47 +2094,47 @@
     学生：「因为产生了新物质」</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L11" s="22" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="n"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>科33</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化和物理变化的区别」</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>R1 AI：在厨房里，切菜和煎蛋分别属于哪种变化？请用‘是否产生新物质’解释你的判断。
     学生：「物理变化和化学变化」
@@ -1522,47 +2148,47 @@
     学生：「因为那些变化只改变了物质的大小形态」</t>
         </is>
       </c>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L12" s="22" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L12" s="24" t="n"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>科39</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化 物理变化」</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能举一个厨房里发生的化学变化的例子，并说说为什么它是化学变化吗？
     学生：「橘子发霉」
@@ -1576,47 +2202,47 @@
     学生：「不会因为是新鲜的」</t>
         </is>
       </c>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L13" s="22" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="n"/>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>科36</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化会产生新物质物理不会」；疑问=「还有什么区别？」</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能举出两个厨房里的物质变化，并用'是否产生新物质'来判断它们各属于哪类变化吗？
     学生：「1把蔬菜切块物理变化2把米饭蒸shu」
@@ -1630,47 +2256,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L14" s="22" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L14" s="24" t="n"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>科23</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学反应和物理反应的区别，化学反应和物理反应分别是什么」</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请举出一个厨房里发生的物理变化的例子，并解释为什么它是物理变化。
     学生：「冰箱里的冰块慢慢融化，物理变化，只改变了形体」
@@ -1684,47 +2310,47 @@
     学生：「谁可以冰冻重新变成冰，酸奶变不回去，因为产生新物质」</t>
         </is>
       </c>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L15" s="22" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="n"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>科30</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学反应 和 物理反应的区别」</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到学到了化学反应和物理反应的区别，请举一个你在厨房里观察到的化学变化的例子，并说明为什么你认为它是化学变化？
     学生：「慢慢融化的bin」
@@ -1738,47 +2364,47 @@
     学生：「有       物理变化」</t>
         </is>
       </c>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="19" t="n"/>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L16" s="22" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L16" s="24" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>科26</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「关于宇宙的变化」；疑问=「没有」</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到了宇宙的变化，那在厨房里，你见过哪些物质变化？请举一个例子，并说明它是否产生了新物质。
     学生：「火」
@@ -1792,47 +2418,47 @@
     学生：「发生了蓬大」</t>
         </is>
       </c>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L17" s="22" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>科18</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化会产生新物质物理变化不会」</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请举一个厨房里发生的化学变化的例子，并说说为什么你认为它是化学变化？
     学生：「米饭正好因为会又香气」
@@ -1846,47 +2472,47 @@
     学生：「会变大」</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L18" s="22" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L18" s="24" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>科19</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「产生新物质是化学变化 没有产生是物理变化」</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>R1 AI：厨房里经常发生物质变化，比如苹果切开后变色，你能解释一下这是物理变化还是化学变化，为什么？
     学生：「产生」
@@ -1900,47 +2526,47 @@
     学生：「产生了」</t>
         </is>
       </c>
-      <c r="G19" s="19" t="n"/>
-      <c r="H19" s="19" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="19" t="n"/>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L19" s="22" t="n"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>科29</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学的概念」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到学习了化学的概念，请以厨房里的苹果切开后变色为例，解释为什么这是化学变化，并说明判断的关键标准是什么。
     学生：「这是氧化」
@@ -1954,48 +2580,48 @@
     学生：「气味」</t>
         </is>
       </c>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="19" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="19" t="n"/>
-      <c r="K20" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L20" s="22" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L20" s="24" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>科3</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物理
 和化学变化」</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在厨房里见过哪些物质变化？请举出一个物理变化和一个化学变化的例子，并说说你是怎么判断它们有没有产生新物质的。
     学生：「和面时，没有新物质」
@@ -2009,47 +2635,47 @@
     学生：「不能，可以说明。因为变不回去」</t>
         </is>
       </c>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="19" t="n"/>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L21" s="22" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="n"/>
     </row>
     <row r="22" ht="150" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>科1</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「.;;;;;;_GDRO」；疑问=「3UIT8R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7R7A」</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请回想你在厨房里见过的一种物质变化，并举一个例子，说说这个变化是物理变化还是化学变化，为什么这样判断？
     学生：「面包发霉 科学变化 因为科学」
@@ -2063,48 +2689,48 @@
     学生：「变成了五颜六色 气味有点酸」</t>
         </is>
       </c>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="19" t="n"/>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L22" s="22" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L22" s="24" t="n"/>
     </row>
     <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>科21</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化产反应会产生新物质。
 物理反应仅改变形态。」；疑问=「。」</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在反思中提到化学变化会产生新物质，物理变化只改变形态。请从厨房里找一个具体的例子，说说你怎样判断它是物理变化还是化学变化？
     学生：「米饭」
@@ -2118,47 +2744,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="19" t="n"/>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L23" s="22" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="n"/>
     </row>
     <row r="24" ht="150" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>科31</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物质有化学变化和物理变化」；疑问=「为什么会发生物理或化学变化」</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你能从厨房里找出一个物理变化和一个化学变化的例子，并说明你是根据什么判断它们是物理变化或化学变化的吗？
     学生：「苹果发霉是化学变化」
@@ -2172,47 +2798,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="19" t="n"/>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L24" s="24" t="n"/>
     </row>
     <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>科24</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「生物的多样性」</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在厨房里见过哪些物质变化？请举一个产生了新物质和一个没有产生新物质的例子，并说说这样分类的理由。
     学生：「冰箱将」
@@ -2226,47 +2852,47 @@
     学生：「没有」</t>
         </is>
       </c>
-      <c r="G25" s="19" t="n"/>
-      <c r="H25" s="19" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="19" t="n"/>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="n"/>
     </row>
     <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>科7</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我们的生活中有关于化学或物理的变化」</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到生活中有化学或物理变化，能请你从厨房里举一个例子，并说说它是哪种变化吗？
     学生：「厨房中演示物理变化」
@@ -2280,47 +2906,47 @@
     学生：「是」</t>
         </is>
       </c>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="19" t="n"/>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L26" s="22" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L26" s="24" t="n"/>
     </row>
     <row r="27" ht="150" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>科27</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了化学变化，和物理变化」</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在厨房里观察过哪些物理变化和化学变化？请分别举一个例子，并解释你是用什么标准来区分的。
     学生：「冰块融化，苹果变质，我是通过大小形态，气味颜色区分的」
@@ -2334,47 +2960,47 @@
     学生：「不能，只是变化外观，形态只能算作物理变化但是物理变化不会有新物质」</t>
         </is>
       </c>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L27" s="22" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="n"/>
     </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>科35</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我们的生活都离不开物质  上课使用的课本和桌子和各种食物 都是由物质构成的   各种动植物  包括我们的身体  也是由物质构成的」</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到厨房里有各种食物和用具这些物质，那这些物质在厨房里会发生变化吗？请举一个你见过的例子，并判断它有没有产生新物质。
     学生：「有一些物质会发生变化   比如米饭」
@@ -2388,47 +3014,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L28" s="22" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="n"/>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>科34</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物理变化和化学变化的区别」</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到学习了物理变化和化学变化的区别，那么在厨房里烧开水时，水变成水蒸气，这属于什么变化？为什么？
     学生：「属于物理变化。因为shui'bian'c」
@@ -2442,48 +3068,48 @@
     学生：「属于化学变化，颜色发生了变化，产sh」</t>
         </is>
       </c>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L29" s="22" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="n"/>
     </row>
     <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>科28</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「产生了新物质是化学变化，会发光发热，有气味，会变色。
 物理变化是没有产生变化，形态，大小改变。」；疑问=「柠檬水为什么会将碘伏变色？」</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你说化学变化会变色，那柠檬水让碘伏变色属于化学变化吗？请解释你的判断依据。
     学生：「属于。因为它变色了」
@@ -2497,48 +3123,48 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L30" s="22" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L30" s="24" t="n"/>
     </row>
     <row r="31" ht="150" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>科13</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化：产生了新物质（大部分发光·发热，有气味有颜色）
 物理变化：没有产生新物质（形态大小）」</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到化学变化会产生新物质，那么苹果切开放一段时间后变色，这是化学变化吗？请解释你的判断依据。
     学生：「是，会变色」
@@ -2552,47 +3178,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L31" s="22" t="n"/>
+      <c r="G31" s="21" t="n"/>
+      <c r="H31" s="21" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="n"/>
     </row>
     <row r="32" ht="150" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>科25</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「产生新物质是化学变化；没产生是物理变化」</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请判断盐在水中溶解属于物理变化还是化学变化，并解释为什么。
     学生：「是物理反应，因为没有产生新物质」
@@ -2606,47 +3232,47 @@
     学生：「气味，颜色没有变化」</t>
         </is>
       </c>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L32" s="22" t="n"/>
+      <c r="G32" s="21" t="n"/>
+      <c r="H32" s="21" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L32" s="24" t="n"/>
     </row>
     <row r="33" ht="150" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>科9</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「物质有化学变化和物理变化：化学变化会产生新物质，大部分发光发热有气味；物理变化不改变物质。」</t>
         </is>
       </c>
-      <c r="F33" s="18" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在反思中提到化学变化大部分发光发热有气味。那么，如果把水烧开变成水蒸气，这个过程中水不停地冒泡，看起来也很剧烈，你认为它是化学变化吗？请根据是否产生新物质来解释。
     学生：「我认为水是物理变化：因为物质没有改变只是」
@@ -2660,47 +3286,47 @@
     学生：「水蒸气冷却收集会成为水，不改变物质，z'g」</t>
         </is>
       </c>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L33" s="22" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="n"/>
     </row>
     <row r="34" ht="150" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>科10</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「学到了关于物质的变化 比如经过化学变化可以产生新物质大部分有颜色会发光 还有物理变化但是它产不能产生新物质」；疑问=「？还能经过什么样的变化可以产生成新物质」</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请你举一个在厨房里观察到的物质变化的例子，并判断它属于物理变化还是化学变化，说说你判断的理由。
     学生：「咬过后的苹果」
@@ -2714,47 +3340,47 @@
     学生：「我觉得是 所以是化学变化」</t>
         </is>
       </c>
-      <c r="G34" s="19" t="n"/>
-      <c r="H34" s="19" t="n"/>
-      <c r="I34" s="20" t="n"/>
-      <c r="J34" s="19" t="n"/>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L34" s="22" t="n"/>
+      <c r="G34" s="21" t="n"/>
+      <c r="H34" s="21" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="21" t="n"/>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L34" s="24" t="n"/>
     </row>
     <row r="35" ht="150" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>科37</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学和物理变化」</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>R1 AI：请举出一个厨房里发生的物理变化和一个化学变化的例子，并说说你是根据什么标准来区分的？
     学生：「产生了新物质是化学变化」
@@ -2768,47 +3394,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L35" s="22" t="n"/>
+      <c r="G35" s="21" t="n"/>
+      <c r="H35" s="21" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="n"/>
     </row>
     <row r="36" ht="150" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>科32</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「关于宇宙的许多知识，比如银河系及河外星系」；疑问=「无」</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在反思中提到学了银河系的知识，但在我们的厨房里也有物质变化。你能举一个你在厨房见过的变化，并用‘是否产生新物质’判断它是物理变化还是化学变化吗？
     学生：「米经过蒸煮才能shu」
@@ -2822,48 +3448,48 @@
     学生：「能，因为大部分化学变化是产生了发热，有气味的现象，米饭正如此」</t>
         </is>
       </c>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="20" t="n"/>
-      <c r="J36" s="19" t="n"/>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L36" s="22" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L36" s="24" t="n"/>
     </row>
     <row r="37" ht="150" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>科20</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学变化    产生了新物质
 物理变化   没有产生新物质」</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你把盐放进水里搅拌，盐消失了。这个变化是物理变化还是化学变化？请用“是否产生新物质”来解释你的判断。
     学生：「物理变化   不会」
@@ -2877,47 +3503,47 @@
     学生：「因为一直以来盐的质量没变」</t>
         </is>
       </c>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="20" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L37" s="22" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L37" s="24" t="n"/>
     </row>
     <row r="38" ht="150" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>科6</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「12」</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>R1 AI：糖溶解在水里和铁锅生锈，这两个变化在是否产生新物质上有什么本质区别？
     学生：「不知道」
@@ -2931,47 +3557,47 @@
     学生：「铁锈是铁氧化后的产物」</t>
         </is>
       </c>
-      <c r="G38" s="19" t="n"/>
-      <c r="H38" s="19" t="n"/>
-      <c r="I38" s="20" t="n"/>
-      <c r="J38" s="19" t="n"/>
-      <c r="K38" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L38" s="22" t="n"/>
+      <c r="G38" s="21" t="n"/>
+      <c r="H38" s="21" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="21" t="n"/>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L38" s="24" t="n"/>
     </row>
     <row r="39" ht="150" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>科5</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「科学变化 物理变化 产生新物质」；疑问=「真的产生了吗」</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你反思时提到‘真的产生了吗’，请用一个厨房里的例子解释一下，你在判断有没有新物质产生时遇到了什么困难？
     学生：「橘子发霉了 有」
@@ -2985,47 +3611,47 @@
     学生：「（空）」</t>
         </is>
       </c>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L39" s="22" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="21" t="n"/>
+      <c r="K39" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L39" s="24" t="n"/>
     </row>
     <row r="40" ht="150" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>科4</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「化学   物理」</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你在反思中提到了“化学”和“物理”，那么在厨房里你观察到的哪些变化属于化学变化，哪些属于物理变化？说说你判断的依据是什么。
     学生：「苹果切开后过了」
@@ -3039,47 +3665,47 @@
     学生：「得到认同」</t>
         </is>
       </c>
-      <c r="G40" s="19" t="n"/>
-      <c r="H40" s="19" t="n"/>
-      <c r="I40" s="20" t="n"/>
-      <c r="J40" s="19" t="n"/>
-      <c r="K40" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L40" s="22" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="21" t="n"/>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L40" s="24" t="n"/>
     </row>
     <row r="41" ht="150" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>科2</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>《厨房里的物质变化》</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr">
-        <is>
-          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
-2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
-3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
-4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>《厨房里的物质变化》</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>1) 能列举生活中常见的物理变化（如水结冰、盐溶解）和化学变化（如苹果氧化、铁锅生锈）实例，并用“是否产生新物质”这一核心标准对物质变化进行初步分类。
+2) 通过观察厨房中水、食盐、苹果等物质的状态与特征，运用比较、分析、归纳的方法，自主建构物理变化和化学变化的概念模型。
+3) 能够针对厨房中的特定现象（如切菜、烧水、煎蛋），准确描述其变化前后的特征，并能基于观察提出可探究方法。
+4) 在探究活动中体会科学与生活的紧密联系，感受物质变化的奇妙，初步树立安全用火、合理处理厨余垃圾的生活责任意识。</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>目标1：学到=「我学到了物质的变化有化学变化也有物理变化，化学变化是产生了新的物质，物理变化是没有产生新物质」</t>
         </is>
       </c>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>R1 AI：你提到化学变化产生新物质，物理变化没有，那么你能从厨房里找出一个物理变化和一个化学变化的例子，并用这个标准解释为什么这样分类吗？
     学生：「比如化学变化有鸡蛋从神的变化成sh」
@@ -3093,16 +3719,16 @@
     学生：「比如它产生了发热和蛋白从变白」</t>
         </is>
       </c>
-      <c r="G41" s="19" t="n"/>
-      <c r="H41" s="19" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="19" t="n"/>
-      <c r="K41" s="21" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="L41" s="22" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="21" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="21" t="n"/>
+      <c r="K41" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="L41" s="24" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
